--- a/data/trans_dic/P2C_R1-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R1-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,17</t>
+          <t>0,12; 1,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,52 +727,52 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,62</t>
+          <t>0,15; 1,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,61; 39,47</t>
+          <t>24,52; 38,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,64</t>
+          <t>0,31; 1,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,63</t>
+          <t>0,35; 1,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,57</t>
+          <t>0,16; 1,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,18; 37,71</t>
+          <t>29,05; 38,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,1</t>
+          <t>0,3; 1,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,27</t>
+          <t>0,38; 1,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,19</t>
+          <t>0,26; 1,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,35; 36,73</t>
+          <t>28,96; 36,41</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,36</t>
+          <t>0,1; 1,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,7</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,92</t>
+          <t>0,57; 1,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,34; 15,29</t>
+          <t>8,29; 15,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,43</t>
+          <t>0,21; 1,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,55</t>
+          <t>0,41; 1,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,16</t>
+          <t>0,25; 1,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 8,1</t>
+          <t>1,76; 8,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,12</t>
+          <t>0,25; 1,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,96</t>
+          <t>0,29; 0,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,26</t>
+          <t>0,48; 1,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,92</t>
+          <t>3,39; 9,93</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,2</t>
+          <t>0,3; 3,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 7,72</t>
+          <t>1,82; 7,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,15</t>
+          <t>0,37; 3,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 28,64</t>
+          <t>6,3; 29,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,3</t>
+          <t>0,35; 3,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,96</t>
+          <t>1,74; 7,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,99</t>
+          <t>1,58; 6,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,26; 17,26</t>
+          <t>7,01; 17,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,52</t>
+          <t>0,54; 2,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,11</t>
+          <t>2,05; 5,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,89</t>
+          <t>1,32; 3,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,78; 20,08</t>
+          <t>8,47; 20,14</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,08</t>
+          <t>0,29; 1,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,3</t>
+          <t>0,45; 1,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,44</t>
+          <t>0,55; 1,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,53; 20,35</t>
+          <t>13,69; 20,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,29</t>
+          <t>0,44; 1,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,7</t>
+          <t>0,77; 1,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,44</t>
+          <t>0,59; 1,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 17,99</t>
+          <t>7,06; 18,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,06</t>
+          <t>0,44; 0,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,3</t>
+          <t>0,71; 1,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,3</t>
+          <t>0,69; 1,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,68; 17,56</t>
+          <t>8,83; 17,42</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>818; 7901</t>
+          <t>816; 7243</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1007; 10092</t>
+          <t>1011; 10095</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>804; 8393</t>
+          <t>802; 7274</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28160; 45164</t>
+          <t>28049; 44509</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2789; 16449</t>
+          <t>3148; 15569</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3705; 17297</t>
+          <t>3760; 17416</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1343; 12361</t>
+          <t>1275; 11925</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>72896; 94199</t>
+          <t>72562; 95842</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4893; 18390</t>
+          <t>5011; 19201</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7261; 22542</t>
+          <t>6711; 22866</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3215; 15533</t>
+          <t>3369; 15884</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>106919; 133794</t>
+          <t>105492; 132601</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>903; 12763</t>
+          <t>898; 13379</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>935; 8152</t>
+          <t>0; 7907</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5878; 21211</t>
+          <t>6271; 21068</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24490; 44897</t>
+          <t>24336; 46415</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2298; 14456</t>
+          <t>2168; 13692</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4984; 18368</t>
+          <t>4906; 18883</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3039; 14243</t>
+          <t>3091; 14555</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9563; 45045</t>
+          <t>9769; 45557</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4764; 21851</t>
+          <t>4942; 20555</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7023; 22519</t>
+          <t>6899; 22666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11709; 29402</t>
+          <t>11135; 28915</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24154; 84277</t>
+          <t>28843; 84379</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1032; 9347</t>
+          <t>878; 9406</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4636; 20027</t>
+          <t>4733; 18566</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>974; 8449</t>
+          <t>985; 8575</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5267; 23037</t>
+          <t>5069; 23329</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1008; 9582</t>
+          <t>1007; 10439</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4723; 18682</t>
+          <t>4685; 20996</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5755; 18727</t>
+          <t>4951; 18810</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6490; 15440</t>
+          <t>6268; 15525</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3104; 14691</t>
+          <t>3120; 14603</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11292; 32257</t>
+          <t>10813; 30951</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7734; 22578</t>
+          <t>7639; 23198</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14919; 34115</t>
+          <t>14385; 34213</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4736; 20677</t>
+          <t>5479; 20075</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9019; 27773</t>
+          <t>9658; 28298</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10542; 27189</t>
+          <t>10456; 27795</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66110; 99430</t>
+          <t>66874; 98891</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10664; 29730</t>
+          <t>10194; 28173</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19089; 42836</t>
+          <t>19350; 44015</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13679; 33539</t>
+          <t>13741; 34225</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>62907; 161127</t>
+          <t>63193; 161664</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19490; 44763</t>
+          <t>18664; 41428</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32516; 60428</t>
+          <t>32950; 61594</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28689; 54952</t>
+          <t>29201; 55021</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>120186; 243054</t>
+          <t>122196; 241155</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R1-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R1-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -722,57 +722,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,41</t>
+          <t>0,14; 1,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,4</t>
+          <t>0,16; 1,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,52; 38,9</t>
+          <t>24,09; 38,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,56</t>
+          <t>0,29; 1,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,64</t>
+          <t>0,39; 1,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,52</t>
+          <t>0,16; 1,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,05; 38,36</t>
+          <t>27,89; 36,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,14</t>
+          <t>0,3; 1,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,29</t>
+          <t>0,38; 1,22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,22</t>
+          <t>0,27; 1,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,96; 36,41</t>
+          <t>28,19; 35,6</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -857,32 +857,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,42</t>
+          <t>0,1; 1,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,68</t>
+          <t>0,08; 0,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,91</t>
+          <t>0,54; 1,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,29; 15,8</t>
+          <t>7,42; 13,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,35</t>
+          <t>0,22; 1,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,6</t>
+          <t>0,42; 1,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 8,19</t>
+          <t>5,69; 10,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,05</t>
+          <t>0,23; 1,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,97</t>
+          <t>0,3; 0,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,24</t>
+          <t>0,49; 1,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 9,93</t>
+          <t>7,04; 10,91</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,22</t>
+          <t>0,3; 3,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 7,15</t>
+          <t>1,8; 7,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,2</t>
+          <t>0,37; 3,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 29,0</t>
+          <t>6,15; 28,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,6</t>
+          <t>0,34; 3,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 7,82</t>
+          <t>1,53; 6,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,02</t>
+          <t>1,59; 5,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,01; 17,36</t>
+          <t>6,34; 16,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,51</t>
+          <t>0,63; 2,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,86</t>
+          <t>2,14; 5,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,99</t>
+          <t>1,34; 3,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,47; 20,14</t>
+          <t>7,23; 18,68</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,05</t>
+          <t>0,32; 1,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,33</t>
+          <t>0,44; 1,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,47</t>
+          <t>0,54; 1,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,69; 20,24</t>
+          <t>12,43; 18,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,22</t>
+          <t>0,46; 1,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,75</t>
+          <t>0,75; 1,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,47</t>
+          <t>0,61; 1,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 18,05</t>
+          <t>14,59; 18,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,98</t>
+          <t>0,44; 0,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,33</t>
+          <t>0,7; 1,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,3</t>
+          <t>0,69; 1,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,83; 17,42</t>
+          <t>14,3; 17,83</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36069</t>
+          <t>38387</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>83232</t>
+          <t>88886</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>119301</t>
+          <t>127273</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>816; 7243</t>
+          <t>820; 7278</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1011; 10095</t>
+          <t>995; 9214</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>802; 7274</t>
+          <t>804; 7483</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28049; 44509</t>
+          <t>30198; 48205</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3148; 15569</t>
+          <t>2923; 14739</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3760; 17416</t>
+          <t>4165; 17290</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1275; 11925</t>
+          <t>1268; 11440</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>72562; 95842</t>
+          <t>77216; 101652</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5011; 19201</t>
+          <t>4987; 19285</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6711; 22866</t>
+          <t>6753; 21770</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3369; 15884</t>
+          <t>3556; 15252</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>105492; 132601</t>
+          <t>113378; 143207</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33653</t>
+          <t>34260</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26005</t>
+          <t>31021</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59658</t>
+          <t>65281</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>898; 13379</t>
+          <t>901; 14039</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 7907</t>
+          <t>938; 8398</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6271; 21068</t>
+          <t>5988; 20682</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24336; 46415</t>
+          <t>25501; 46472</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2168; 13692</t>
+          <t>2197; 14314</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4906; 18883</t>
+          <t>4940; 19009</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3091; 14555</t>
+          <t>3081; 14527</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9769; 45557</t>
+          <t>23215; 41598</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4942; 20555</t>
+          <t>4560; 22211</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6899; 22666</t>
+          <t>7093; 22216</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11135; 28915</t>
+          <t>11369; 29907</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28843; 84379</t>
+          <t>52871; 81952</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11611</t>
+          <t>12181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>10966</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21904</t>
+          <t>23147</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>878; 9406</t>
+          <t>861; 8771</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4733; 18566</t>
+          <t>4671; 19213</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>985; 8575</t>
+          <t>989; 9057</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5069; 23329</t>
+          <t>5591; 25894</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1007; 10439</t>
+          <t>995; 9591</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4685; 20996</t>
+          <t>4115; 18645</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4951; 18810</t>
+          <t>4981; 18466</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6268; 15525</t>
+          <t>6580; 17031</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3120; 14603</t>
+          <t>3691; 14723</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10813; 30951</t>
+          <t>11307; 30847</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7639; 23198</t>
+          <t>7756; 22508</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14385; 34213</t>
+          <t>14070; 36364</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81334</t>
+          <t>84828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>119530</t>
+          <t>130872</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>200864</t>
+          <t>215701</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5479; 20075</t>
+          <t>6058; 20774</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9658; 28298</t>
+          <t>9462; 28409</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10456; 27795</t>
+          <t>10212; 27810</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66874; 98891</t>
+          <t>69593; 104492</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10194; 28173</t>
+          <t>10648; 29809</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19350; 44015</t>
+          <t>18801; 43121</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13741; 34225</t>
+          <t>14176; 33860</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>63193; 161664</t>
+          <t>115012; 148386</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18664; 41428</t>
+          <t>18714; 41885</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32950; 61594</t>
+          <t>32580; 62686</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29201; 55021</t>
+          <t>29090; 54360</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>122196; 241155</t>
+          <t>192743; 240402</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R1-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R1-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
